--- a/sheets/조재수대금교본/검수/배띄워라.xlsx
+++ b/sheets/조재수대금교본/검수/배띄워라.xlsx
@@ -9323,7 +9323,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C5" s="23"/>
@@ -9356,7 +9356,7 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M5" s="23"/>
@@ -9378,7 +9378,7 @@
       <c r="S5" s="23"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="U5" s="23"/>
@@ -9387,15 +9387,11 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -9411,18 +9407,9 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="24"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="24"/>
       <c r="R6" s="21"/>
       <c r="S6" s="24"/>
@@ -9567,19 +9554,11 @@
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -9593,11 +9572,7 @@
         </is>
       </c>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
@@ -9709,8 +9684,7 @@
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-⊏</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="M12" s="23"/>
@@ -9754,7 +9728,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -9793,29 +9767,17 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21"/>
       <c r="K14" s="24"/>
       <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
@@ -9936,11 +9898,7 @@
         </is>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -9948,17 +9906,9 @@
         </is>
       </c>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -9966,11 +9916,7 @@
         </is>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="24"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="24"/>
@@ -10129,17 +10075,9 @@
       <c r="O24" s="24"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="24"/>
-      <c r="R24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R24" s="21"/>
       <c r="S24" s="24"/>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
     <row r="25" ht="79.8" customHeight="true">
@@ -10192,11 +10130,7 @@
       <c r="O26" s="23"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="23"/>
-      <c r="R26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R26" s="21"/>
       <c r="S26" s="23"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
@@ -10258,11 +10192,7 @@
         </is>
       </c>
       <c r="S28" s="24"/>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T28" s="21"/>
       <c r="U28" s="24"/>
     </row>
     <row r="29" ht="79.8" customHeight="true">
@@ -10594,8 +10524,7 @@
       <c r="K40" s="23"/>
       <c r="L40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼
-⊏</t>
+          <t xml:space="preserve">湳∼</t>
         </is>
       </c>
       <c r="M40" s="23"/>
@@ -10644,7 +10573,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K41" s="23"/>
@@ -10668,7 +10597,7 @@
       <c r="S41" s="23"/>
       <c r="T41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="U41" s="23"/>
@@ -10677,37 +10606,21 @@
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D42" s="21"/>
       <c r="E42" s="24"/>
       <c r="F42" s="21"/>
       <c r="G42" s="24"/>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H42" s="21"/>
       <c r="I42" s="24"/>
       <c r="J42" s="21"/>
       <c r="K42" s="24"/>
       <c r="L42" s="21"/>
       <c r="M42" s="24"/>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N42" s="21"/>
       <c r="O42" s="24"/>
       <c r="P42" s="21"/>
       <c r="Q42" s="24"/>
-      <c r="R42" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R42" s="21"/>
       <c r="S42" s="24"/>
       <c r="T42" s="21"/>
       <c r="U42" s="24"/>
@@ -10839,11 +10752,7 @@
         </is>
       </c>
       <c r="C46" s="24"/>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D46" s="21"/>
       <c r="E46" s="24"/>
       <c r="F46" s="21" t="inlineStr">
         <is>
@@ -10851,29 +10760,13 @@
         </is>
       </c>
       <c r="G46" s="24"/>
-      <c r="H46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H46" s="21"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J46" s="21"/>
       <c r="K46" s="24"/>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L46" s="21"/>
       <c r="M46" s="24"/>
-      <c r="N46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N46" s="21"/>
       <c r="O46" s="24"/>
       <c r="P46" s="21" t="inlineStr">
         <is>
@@ -10881,11 +10774,7 @@
         </is>
       </c>
       <c r="Q46" s="24"/>
-      <c r="R46" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R46" s="21"/>
       <c r="S46" s="24"/>
       <c r="T46" s="21" t="inlineStr">
         <is>
@@ -11036,7 +10925,7 @@
       <c r="C49" s="23"/>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E49" s="23"/>
@@ -11069,7 +10958,7 @@
       <c r="M49" s="23"/>
       <c r="N49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O49" s="23"/>
@@ -11106,24 +10995,16 @@
       <c r="C50" s="24"/>
       <c r="D50" s="21"/>
       <c r="E50" s="24"/>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F50" s="21"/>
       <c r="G50" s="24"/>
       <c r="H50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="I50" s="24"/>
-      <c r="J50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J50" s="21"/>
       <c r="K50" s="24"/>
       <c r="L50" s="21" t="inlineStr">
         <is>
@@ -11134,15 +11015,11 @@
       <c r="M50" s="24"/>
       <c r="N50" s="21"/>
       <c r="O50" s="24"/>
-      <c r="P50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P50" s="21"/>
       <c r="Q50" s="24"/>
       <c r="R50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–ﾉ
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -11292,11 +11169,7 @@
     </row>
     <row r="54" ht="79.8" customHeight="true">
       <c r="A54" s="0"/>
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B54" s="21"/>
       <c r="C54" s="24"/>
       <c r="D54" s="21" t="inlineStr">
         <is>
@@ -11304,11 +11177,7 @@
         </is>
       </c>
       <c r="E54" s="24"/>
-      <c r="F54" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F54" s="21"/>
       <c r="G54" s="24"/>
       <c r="H54" s="21"/>
       <c r="I54" s="24"/>
@@ -11331,11 +11200,7 @@
         </is>
       </c>
       <c r="O54" s="24"/>
-      <c r="P54" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P54" s="21"/>
       <c r="Q54" s="24"/>
       <c r="R54" s="21"/>
       <c r="S54" s="24"/>
@@ -11537,7 +11402,7 @@
       <c r="P62" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-⊏∼</t>
+∼</t>
         </is>
       </c>
       <c r="Q62" s="23"/>
@@ -11585,11 +11450,7 @@
       <c r="M64" s="24"/>
       <c r="N64" s="21"/>
       <c r="O64" s="24"/>
-      <c r="P64" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P64" s="21"/>
       <c r="Q64" s="24"/>
       <c r="R64" s="21" t="inlineStr">
         <is>
@@ -11622,7 +11483,7 @@
       <c r="O65" s="22"/>
       <c r="P65" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="Q65" s="22"/>
@@ -11692,7 +11553,7 @@
       <c r="Q67" s="23"/>
       <c r="R67" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="S67" s="23"/>
@@ -11724,11 +11585,7 @@
       <c r="Q68" s="24"/>
       <c r="R68" s="21"/>
       <c r="S68" s="24"/>
-      <c r="T68" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T68" s="21"/>
       <c r="U68" s="24"/>
     </row>
     <row r="69" ht="79.8" customHeight="true">

--- a/sheets/조재수대금교본/검수/배띄워라.xlsx
+++ b/sheets/조재수대금교본/검수/배띄워라.xlsx
@@ -9323,7 +9323,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="C5" s="23"/>
@@ -9356,7 +9356,7 @@
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M5" s="23"/>
@@ -9378,7 +9378,7 @@
       <c r="S5" s="23"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="U5" s="23"/>
@@ -9391,7 +9391,7 @@
       <c r="E6" s="24"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ﾉ
 △</t>
         </is>
       </c>
@@ -9409,7 +9409,11 @@
       <c r="M6" s="24"/>
       <c r="N6" s="21"/>
       <c r="O6" s="24"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="Q6" s="24"/>
       <c r="R6" s="21"/>
       <c r="S6" s="24"/>
@@ -9684,7 +9688,8 @@
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼</t>
+          <t xml:space="preserve">湳∼
+⊏</t>
         </is>
       </c>
       <c r="M12" s="23"/>
@@ -9728,7 +9733,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -10524,7 +10529,8 @@
       <c r="K40" s="23"/>
       <c r="L40" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∼</t>
+          <t xml:space="preserve">湳∼
+⊏</t>
         </is>
       </c>
       <c r="M40" s="23"/>
@@ -10573,7 +10579,7 @@
       <c r="I41" s="23"/>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="K41" s="23"/>
@@ -10597,7 +10603,7 @@
       <c r="S41" s="23"/>
       <c r="T41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="U41" s="23"/>
@@ -10925,7 +10931,7 @@
       <c r="C49" s="23"/>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="E49" s="23"/>
@@ -10958,7 +10964,7 @@
       <c r="M49" s="23"/>
       <c r="N49" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="O49" s="23"/>
@@ -10999,7 +11005,7 @@
       <c r="G50" s="24"/>
       <c r="H50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ﾉ
 △</t>
         </is>
       </c>
@@ -11019,7 +11025,7 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
+          <t xml:space="preserve">–ﾉ
 △</t>
         </is>
       </c>
@@ -11402,7 +11408,7 @@
       <c r="P62" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-∼</t>
+⊏∼</t>
         </is>
       </c>
       <c r="Q62" s="23"/>
@@ -11483,7 +11489,7 @@
       <c r="O65" s="22"/>
       <c r="P65" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="Q65" s="22"/>
@@ -11553,7 +11559,7 @@
       <c r="Q67" s="23"/>
       <c r="R67" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="S67" s="23"/>

--- a/sheets/조재수대금교본/검수/배띄워라.xlsx
+++ b/sheets/조재수대금교본/검수/배띄워라.xlsx
@@ -9136,32 +9136,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="79.8" customHeight="true">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="79.8" customHeight="true">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="79.8" customHeight="true">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="79.8" customHeight="true">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -9420,7 +9420,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="79.8" customHeight="true">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -9466,7 +9466,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="79.8" customHeight="true">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -9507,7 +9507,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="79.8" customHeight="true">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -9550,7 +9550,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="79.8" customHeight="true">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="79.8" customHeight="true">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="79.8" customHeight="true">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="79.8" customHeight="true">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="79.8" customHeight="true">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -9791,7 +9791,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="79.8" customHeight="true">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -9829,7 +9829,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="79.8" customHeight="true">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -9867,7 +9867,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="79.8" customHeight="true">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -9895,7 +9895,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="79.8" customHeight="true">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="71.43" customHeight="true">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="79.8" customHeight="true">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="79.8" customHeight="true">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="79.8" customHeight="true">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -10062,7 +10062,7 @@
       <c r="T23" s="21"/>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="79.8" customHeight="true">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -10085,7 +10085,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="79.8" customHeight="true">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="79.8" customHeight="true">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="79.8" customHeight="true">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -10172,7 +10172,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="79.8" customHeight="true">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -10200,7 +10200,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="79.8" customHeight="true">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="79.8" customHeight="true">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="U30" s="23"/>
     </row>
-    <row r="31" ht="79.8" customHeight="true">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -10284,7 +10284,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="79.8" customHeight="true">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -10307,7 +10307,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="79.8" customHeight="true">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -10330,7 +10330,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="79.8" customHeight="true">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -10353,7 +10353,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="79.8" customHeight="true">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -10376,7 +10376,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="79.8" customHeight="true">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -10410,7 +10410,7 @@
     <row r="37" ht="6.0" customHeight="true">
       <c r="A37" s="0"/>
     </row>
-    <row r="38" ht="71.43" customHeight="true">
+    <row r="38" ht="80.0" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="20" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
       <c r="T38" s="20"/>
       <c r="U38" s="20"/>
     </row>
-    <row r="39" ht="79.8" customHeight="true">
+    <row r="39" ht="89.42" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="79.8" customHeight="true">
+    <row r="40" ht="89.42" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="U40" s="23"/>
     </row>
-    <row r="41" ht="79.8" customHeight="true">
+    <row r="41" ht="89.42" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="79.8" customHeight="true">
+    <row r="42" ht="89.42" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -10631,7 +10631,7 @@
       <c r="T42" s="21"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" ht="79.8" customHeight="true">
+    <row r="43" ht="89.42" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21"/>
       <c r="C43" s="22"/>
@@ -10674,7 +10674,7 @@
       <c r="T43" s="21"/>
       <c r="U43" s="22"/>
     </row>
-    <row r="44" ht="79.8" customHeight="true">
+    <row r="44" ht="89.42" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21"/>
       <c r="C44" s="23"/>
@@ -10717,7 +10717,7 @@
       <c r="T44" s="21"/>
       <c r="U44" s="23"/>
     </row>
-    <row r="45" ht="79.8" customHeight="true">
+    <row r="45" ht="89.42" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="23"/>
@@ -10750,7 +10750,7 @@
       <c r="T45" s="21"/>
       <c r="U45" s="23"/>
     </row>
-    <row r="46" ht="79.8" customHeight="true">
+    <row r="46" ht="89.42" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="U46" s="24"/>
     </row>
-    <row r="47" ht="79.8" customHeight="true">
+    <row r="47" ht="89.42" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="U47" s="22"/>
     </row>
-    <row r="48" ht="79.8" customHeight="true">
+    <row r="48" ht="89.42" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="U48" s="23"/>
     </row>
-    <row r="49" ht="79.8" customHeight="true">
+    <row r="49" ht="89.42" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="U49" s="23"/>
     </row>
-    <row r="50" ht="79.8" customHeight="true">
+    <row r="50" ht="89.42" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
       <c r="T50" s="21"/>
       <c r="U50" s="24"/>
     </row>
-    <row r="51" ht="79.8" customHeight="true">
+    <row r="51" ht="89.42" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
       <c r="T51" s="21"/>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="79.8" customHeight="true">
+    <row r="52" ht="89.42" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
       <c r="T52" s="21"/>
       <c r="U52" s="23"/>
     </row>
-    <row r="53" ht="79.8" customHeight="true">
+    <row r="53" ht="89.42" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="23"/>
@@ -11173,7 +11173,7 @@
       <c r="T53" s="21"/>
       <c r="U53" s="23"/>
     </row>
-    <row r="54" ht="79.8" customHeight="true">
+    <row r="54" ht="89.42" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="24"/>
@@ -11220,7 +11220,7 @@
     <row r="55" ht="6.0" customHeight="true">
       <c r="A55" s="0"/>
     </row>
-    <row r="56" ht="71.43" customHeight="true">
+    <row r="56" ht="80.0" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="20" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
       <c r="T56" s="20"/>
       <c r="U56" s="20"/>
     </row>
-    <row r="57" ht="79.8" customHeight="true">
+    <row r="57" ht="89.42" customHeight="true">
       <c r="A57" s="0"/>
       <c r="B57" s="21"/>
       <c r="C57" s="22"/>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="U57" s="22"/>
     </row>
-    <row r="58" ht="79.8" customHeight="true">
+    <row r="58" ht="89.42" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="21"/>
       <c r="C58" s="23"/>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="U58" s="23"/>
     </row>
-    <row r="59" ht="79.8" customHeight="true">
+    <row r="59" ht="89.42" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21"/>
       <c r="C59" s="23"/>
@@ -11331,7 +11331,7 @@
       <c r="T59" s="21"/>
       <c r="U59" s="23"/>
     </row>
-    <row r="60" ht="79.8" customHeight="true">
+    <row r="60" ht="89.42" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="24"/>
@@ -11358,7 +11358,7 @@
       <c r="T60" s="21"/>
       <c r="U60" s="24"/>
     </row>
-    <row r="61" ht="79.8" customHeight="true">
+    <row r="61" ht="89.42" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="22"/>
@@ -11389,7 +11389,7 @@
       <c r="T61" s="21"/>
       <c r="U61" s="22"/>
     </row>
-    <row r="62" ht="79.8" customHeight="true">
+    <row r="62" ht="89.42" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="23"/>
@@ -11417,7 +11417,7 @@
       <c r="T62" s="21"/>
       <c r="U62" s="23"/>
     </row>
-    <row r="63" ht="79.8" customHeight="true">
+    <row r="63" ht="89.42" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21"/>
       <c r="C63" s="23"/>
@@ -11440,7 +11440,7 @@
       <c r="T63" s="21"/>
       <c r="U63" s="23"/>
     </row>
-    <row r="64" ht="79.8" customHeight="true">
+    <row r="64" ht="89.42" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21"/>
       <c r="C64" s="24"/>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="U64" s="24"/>
     </row>
-    <row r="65" ht="79.8" customHeight="true">
+    <row r="65" ht="89.42" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="U65" s="22"/>
     </row>
-    <row r="66" ht="79.8" customHeight="true">
+    <row r="66" ht="89.42" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="23"/>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="U66" s="23"/>
     </row>
-    <row r="67" ht="79.8" customHeight="true">
+    <row r="67" ht="89.42" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="23"/>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="U67" s="23"/>
     </row>
-    <row r="68" ht="79.8" customHeight="true">
+    <row r="68" ht="89.42" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21"/>
       <c r="C68" s="24"/>
@@ -11594,7 +11594,7 @@
       <c r="T68" s="21"/>
       <c r="U68" s="24"/>
     </row>
-    <row r="69" ht="79.8" customHeight="true">
+    <row r="69" ht="89.42" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="22"/>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="U69" s="22"/>
     </row>
-    <row r="70" ht="79.8" customHeight="true">
+    <row r="70" ht="89.42" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="23"/>
@@ -11644,7 +11644,7 @@
       <c r="T70" s="21"/>
       <c r="U70" s="23"/>
     </row>
-    <row r="71" ht="79.8" customHeight="true">
+    <row r="71" ht="89.42" customHeight="true">
       <c r="A71" s="0"/>
       <c r="B71" s="21"/>
       <c r="C71" s="23"/>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="U71" s="23"/>
     </row>
-    <row r="72" ht="79.8" customHeight="true">
+    <row r="72" ht="89.42" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="21"/>
       <c r="C72" s="24"/>
@@ -11708,7 +11708,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="18" max="16383" man="1"/>
     <brk id="36" max="16383" man="1"/>
